--- a/results/-1Fold_external.xlsx
+++ b/results/-1Fold_external.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,40 +466,45 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Train Ratio</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Layers</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Hidden Dim</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Activation</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>C-index</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>C-index IPCW</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>IBS</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
@@ -513,7 +518,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>decouple</t>
+          <t>deephit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -531,33 +536,36 @@
         <v>42</v>
       </c>
       <c r="G2" t="n">
+        <v>1095.75</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
       <c r="I2" t="n">
-        <v>2048</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>leaky_relu</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>0.6675859684982566</v>
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
       </c>
       <c r="L2" t="n">
-        <v>0.6656560930410321</v>
+        <v>0.6631297342791872</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7303251154686745</v>
+        <v>0.6614482985521891</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1452811349035757</v>
+        <v>0.7187981454482436</v>
       </c>
       <c r="O2" t="n">
-        <v>14.64147853851318</v>
+        <v>0.1538733985799662</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.5370614329973856</v>
       </c>
     </row>
     <row r="3">
@@ -568,7 +576,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>decouple</t>
+          <t>deephit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -586,33 +594,36 @@
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>1095.75</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>2048</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>leaky_relu</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0.6725156306360467</v>
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
       </c>
       <c r="L3" t="n">
-        <v>0.6705611005298499</v>
+        <v>0.6493026331609956</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7379304240864898</v>
+        <v>0.6481446698055119</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1435390666310039</v>
+        <v>0.6774869192677774</v>
       </c>
       <c r="O3" t="n">
-        <v>14.65407498677572</v>
+        <v>0.1468842002349512</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.5497429370880127</v>
       </c>
     </row>
     <row r="4">
@@ -623,7 +634,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>decouple</t>
+          <t>deepsurv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -641,33 +652,36 @@
         <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>30.4375</v>
+        <v>1095.75</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2048</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>leaky_relu</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.6718468197667428</v>
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
       </c>
       <c r="L4" t="n">
-        <v>0.6699319584447553</v>
+        <v>0.6667818925093183</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7345163872183048</v>
+        <v>0.664851207433518</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1469912528315928</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>7.833415508270264</v>
+        <v>0.2846381672399507</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.750398476918538</v>
       </c>
     </row>
     <row r="5">
@@ -678,7 +692,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>decouple</t>
+          <t>deepsurv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,33 +710,36 @@
         <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>91.3125</v>
+        <v>1095.75</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>2048</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>leaky_relu</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0.6719369965131659</v>
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
       </c>
       <c r="L5" t="n">
-        <v>0.6700593461247139</v>
+        <v>0.6474615245881928</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7328162682185519</v>
+        <v>0.6461354266663442</v>
       </c>
       <c r="N5" t="n">
-        <v>0.143848627596052</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>4.921571890513103</v>
+        <v>0.2851280096433711</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4.800751050313314</v>
       </c>
     </row>
     <row r="6">
@@ -733,7 +750,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>decouple</t>
+          <t>nll</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -751,33 +768,36 @@
         <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>182.625</v>
+        <v>1095.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2048</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>leaky_relu</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.6724479980762295</v>
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
       </c>
       <c r="L6" t="n">
-        <v>0.670560750972189</v>
+        <v>0.6498587230972707</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7283333818259925</v>
+        <v>0.6477958111563038</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1418843577424355</v>
+        <v>0.7185924084756289</v>
       </c>
       <c r="O6" t="n">
-        <v>4.136125405629476</v>
+        <v>0.1680521423764997</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.7001132369041443</v>
       </c>
     </row>
     <row r="7">
@@ -788,7 +808,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>decouple</t>
+          <t>nll</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -806,33 +826,36 @@
         <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>365.25</v>
+        <v>1095.75</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>2048</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>leaky_relu</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0.672184982565829</v>
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
       </c>
       <c r="L7" t="n">
-        <v>0.6703001105047649</v>
+        <v>0.6341529397619334</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7287474396644995</v>
+        <v>0.6324348916905331</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1427784915839577</v>
+        <v>0.6826448507777523</v>
       </c>
       <c r="O7" t="n">
-        <v>3.430082718531291</v>
+        <v>0.1586713624313262</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.7173070907592773</v>
       </c>
     </row>
     <row r="8">
@@ -864,29 +887,32 @@
         <v>1095.75</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>2048</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>leaky_relu</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>0.6708473608272214</v>
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
       </c>
       <c r="L8" t="n">
+        <v>0.670847360827221</v>
+      </c>
+      <c r="M8" t="n">
         <v>0.6689780784228232</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>0.7340936749667315</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>0.1430603095390974</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>2.466720422108968</v>
       </c>
     </row>
@@ -916,33 +942,558 @@
         <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>1826.25</v>
+        <v>1095.75</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="I9" t="n">
-        <v>2048</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>leaky_relu</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0.6691114584585788</v>
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
       </c>
       <c r="L9" t="n">
-        <v>0.6672190100288481</v>
+        <v>0.657613923289648</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7177298071003549</v>
+        <v>0.6560585286331767</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1428144833167877</v>
+        <v>0.698252954486866</v>
       </c>
       <c r="O9" t="n">
-        <v>2.109362761179606</v>
+        <v>0.1460423014360021</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.014553149541219</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>deephit</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42</v>
+      </c>
+      <c r="G10" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.657403510881327</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.6556103176074863</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.7153869310568146</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.135425921039935</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.7443938255310059</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>deephit</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" t="n">
+        <v>42</v>
+      </c>
+      <c r="G11" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.621295238667789</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.6199809451572027</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.6890802504447356</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.141347726548649</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.7618143161137899</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>nll</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G12" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.623008596849826</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.6209385363989109</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6964901346623209</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1416386141604265</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.115681608517965</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>nll</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42</v>
+      </c>
+      <c r="G13" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.57485421425995</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.5733080712978441</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.6584196529061812</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.1434588194132335</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.133378465970357</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>deepsurv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42</v>
+      </c>
+      <c r="G14" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6667818925093183</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.664851207433518</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2967769227942333</v>
+      </c>
+      <c r="P14" t="n">
+        <v>4.750398476918538</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>deepsurv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42</v>
+      </c>
+      <c r="G15" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6474615245881928</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.6461354266663442</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.2971518871283705</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.800751050313314</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>decouple</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42</v>
+      </c>
+      <c r="G16" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6640164722856799</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.6623838089287927</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.7180874779310602</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.1544379955454476</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4.00783125559489</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>decouple</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G17" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.673319706624985</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.6714064871377047</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.7296611866986386</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.1430804772570685</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3.4930100440979</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>external</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pchazard</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42</v>
+      </c>
+      <c r="G18" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>leaky_relu</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5781080918600456</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.5761173034802907</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.608663680858018</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.2954924888557099</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.952392737070719</v>
       </c>
     </row>
   </sheetData>
